--- a/www/专普票区分表模板.xlsx
+++ b/www/专普票区分表模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\棱星数据\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A32AAF-5630-474C-9D6B-82A43637A52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76FB3CB-734E-4700-B491-0DA07726FBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E985C30-924C-4591-846C-C630C501C439}"/>
+    <workbookView xWindow="8232" yWindow="3048" windowWidth="14076" windowHeight="9192" xr2:uid="{6E985C30-924C-4591-846C-C630C501C439}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -39,9 +39,6 @@
     <t>专用发票</t>
   </si>
   <si>
-    <t>名称</t>
-  </si>
-  <si>
     <t>阿克苏辉诺医疗器械有限公司</t>
   </si>
   <si>
@@ -52,6 +49,10 @@
   </si>
   <si>
     <t>开票要求</t>
+  </si>
+  <si>
+    <t>客户名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -426,18 +427,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
         <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -456,7 +457,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
@@ -476,7 +477,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62E4B9A2-8942-469F-84DD-FB3C2C6F1379}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0C42C3A-932E-4C9F-A7D3-7E0B9EE88656}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>